--- a/perfume_catalog.xlsx
+++ b/perfume_catalog.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C128"/>
+  <dimension ref="A1:C127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2285,7 +2285,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Fragrance World</t>
+          <t>Maison Alhambra</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2295,14 +2295,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Barakkat Rouge 540; Barakkat Satin Oud; Imperium; Suits; Ebony Fume; Jack of Clubs; Spectre Ghost; Cocktail Intense; After Effect; Star Men Nebula; Royal Blend; Apex; Mocha Wood; Proud of You Absolute</t>
+          <t>Tobacco Touch; Porto Neroli; Kismet Angel; Kismet Magic; Woody Oud; Bright Peach; Amber &amp; Leather; Lovely Cherie; Fabulo Intense; Toscano Leather; The Tux; Jorge di Profumo; Baroque Rouge 540</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Maison Alhambra</t>
+          <t>The Body Shop</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2312,48 +2312,48 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tobacco Touch; Porto Neroli; Kismet Angel; Kismet Magic; Woody Oud; Bright Peach; Amber &amp; Leather; Lovely Cherie; Fabulo Intense; Toscano Leather; The Tux; Jorge di Profumo; Baroque Rouge 540</t>
+          <t>White Musk; Black Musk; British Rose; Moringa; Shea; Satsuma; Japanese Cherry Blossom; Vanilla; White Musk L'Eau; Blue Musk; Arber; Activist</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>The Body Shop</t>
+          <t>Bath &amp; Body Works</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BBW</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>White Musk; Black Musk; British Rose; Moringa; Shea; Satsuma; Japanese Cherry Blossom; Vanilla; White Musk L'Eau; Blue Musk; Arber; Activist</t>
+          <t>Japanese Cherry Blossom; Into the Night; A Thousand Wishes; Gingham; Warm Vanilla Sugar; Ocean; Champagne Toast; In the Stars; You're the One; Mahogany Teakwood; Butterfly; Dream Bright; Pure Wonder</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Bath &amp; Body Works</t>
+          <t>Avon</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BBW</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Japanese Cherry Blossom; Into the Night; A Thousand Wishes; Gingham; Warm Vanilla Sugar; Ocean; Champagne Toast; In the Stars; You're the One; Mahogany Teakwood; Butterfly; Dream Bright; Pure Wonder</t>
+          <t>Far Away; Today; Little Black Dress; Luck; Attraction; Mesmerize; Imari; Rare Gold; Rare Pearls; Perceive; Incandessence; Eve Truth; Black Suede; Wild Country</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Avon</t>
+          <t>Oriflame</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2363,14 +2363,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Far Away; Today; Little Black Dress; Luck; Attraction; Mesmerize; Imari; Rare Gold; Rare Pearls; Perceive; Incandessence; Eve Truth; Black Suede; Wild Country</t>
+          <t>Eclat; Giordani Gold; Miss Giordani; Possess; Venture; Volare; Love Potion; Amber Elixir; Divine; Glacier; Signature; So Fever; Northern Glow</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Oriflame</t>
+          <t>Mary Kay</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2380,14 +2380,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Eclat; Giordani Gold; Miss Giordani; Possess; Venture; Volare; Love Potion; Amber Elixir; Divine; Glacier; Signature; So Fever; Northern Glow</t>
+          <t>Thinking of You; Journey; Domain; Cityscape; Elige; Illuminea; Belara; Velocity; High Intensity; Live Fearlessly; True Original</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Mary Kay</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2397,14 +2397,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Thinking of You; Journey; Domain; Cityscape; Elige; Illuminea; Belara; Velocity; High Intensity; Live Fearlessly; True Original</t>
+          <t>Dynamic Pulse; Ice Dive; Team Force; Pure Game; Victory League; Moves; Born Original; UEFA Champions League; Get Ready; Fizzy Energy</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2414,14 +2414,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dynamic Pulse; Ice Dive; Team Force; Pure Game; Victory League; Moves; Born Original; UEFA Champions League; Get Ready; Fizzy Energy</t>
+          <t>Urban Musk; Original; Woman; Indigo; Casual; Gold Edition; A Spicy Attitude; On Fire; The Perfume Woman; Brown; Green; Blue</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Revlon</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2431,14 +2431,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Urban Musk; Original; Woman; Indigo; Casual; Gold Edition; A Spicy Attitude; On Fire; The Perfume Woman; Brown; Green; Blue</t>
+          <t>Charlie Red; Charlie Blue; Fire &amp; Ice; Ciara; Jontue; Jean Naté; Charlie White; Charlie Gold; Charlie Silver; Unforgettable; Love Is On</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Revlon</t>
+          <t>Coty</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2448,14 +2448,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Charlie Red; Charlie Blue; Fire &amp; Ice; Ciara; Jontue; Jean Naté; Charlie White; Charlie Gold; Charlie Silver; Unforgettable; Love Is On</t>
+          <t>Aspen; Vanilla Fields; Exclamation; Musk; Gravity; L'Aimant; Wild Musk; Sand &amp; Sable; Stetson; Lady Stetson; Navy; Emeraude</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Coty</t>
+          <t>Yardley</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Aspen; Vanilla Fields; Exclamation; Musk; Gravity; L'Aimant; Wild Musk; Sand &amp; Sable; Stetson; Lady Stetson; Navy; Emeraude</t>
+          <t>English Lavender; Gentleman Classic; April Violets; English Rose; Gold; London Mist; Gentleman Urbane; Gentleman Legacy; Royal Red Roses; Lily of the Valley; Jasmine; Freesia &amp; Bergamot</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Yardley</t>
+          <t>BDK Parfums</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2482,14 +2482,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>English Lavender; Gentleman Classic; April Violets; English Rose; Gold; London Mist; Gentleman Urbane; Gentleman Legacy; Royal Red Roses; Lily of the Valley; Jasmine; Freesia &amp; Bergamot</t>
+          <t>Gris Charnel; Gris Charnel Extrait; Rouge Smoking; 312 Saint-Honore; Pas Ce Soir; Tabac Rose; Wood Jasmin; Citrus Riviera; Velvet Tonka; Bouquet de Hong Kong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BDK Parfums</t>
+          <t>Matiere Premiere</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2499,14 +2499,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Gris Charnel; Gris Charnel Extrait; Rouge Smoking; 312 Saint-Honore; Pas Ce Soir; Tabac Rose; Wood Jasmin; Citrus Riviera; Velvet Tonka; Bouquet de Hong Kong</t>
+          <t>Vanilla Powder; Radical Rose; Parisian Musc; Encens Suave; Santal Austral; Falcon Leather; Apres L Orage; Crystal Saffron; Neroli Oranger; White Yuzu</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Matiere Premiere</t>
+          <t>Atelier des Ors</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2516,14 +2516,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Vanilla Powder; Radical Rose; Parisian Musc; Encens Suave; Santal Austral; Falcon Leather; Apres L Orage; Crystal Saffron; Neroli Oranger; White Yuzu</t>
+          <t>Lune Feline; Rouge Saray; Blue Madeleine; Rose Omeyyade; Cuir Sacre; Nuda Veritas; Santal Carmin; Bois Sikar; Iris Fauve; Larmes du Desert</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Atelier des Ors</t>
+          <t>Argos Fragrances</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2533,14 +2533,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Lune Feline; Rouge Saray; Blue Madeleine; Rose Omeyyade; Cuir Sacre; Nuda Veritas; Santal Carmin; Bois Sikar; Iris Fauve; Larmes du Desert</t>
+          <t>Hera; Apollo; Artemis; Athena; Zeus; Poseidon; Dionysus; Aphrodite; Hermes; Eros</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Argos Fragrances</t>
+          <t>Mind Games</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2550,14 +2550,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Hera; Apollo; Artemis; Athena; Zeus; Poseidon; Dionysus; Aphrodite; Hermes; Eros</t>
+          <t>The King; The Queen; The Bishop; The Knight; The Rook; The Pawn; Checkmate; Gambit; Stalemate; En Passant</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Mind Games</t>
+          <t>Ormonde Jayne</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2567,14 +2567,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>The King; The Queen; The Bishop; The Knight; The Rook; The Pawn; Checkmate; Gambit; Stalemate; En Passant</t>
+          <t>Ormonde Woman; Ormonde Man; Tolu; Champaca; Tiare; Taif Rose; Qi; Frangipani; Nawab of Oudh; Black Gold; Orris Noir; Isfarkand</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ormonde Jayne</t>
+          <t>House of Oud</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2583,23 +2583,6 @@
         </is>
       </c>
       <c r="C127" t="inlineStr">
-        <is>
-          <t>Ormonde Woman; Ormonde Man; Tolu; Champaca; Tiare; Taif Rose; Qi; Frangipani; Nawab of Oudh; Black Gold; Orris Noir; Isfarkand</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>House of Oud</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
         <is>
           <t>Choco Choco; Pink Soul; Waves of Sun; Blue Soul; Touch of Sand; Tobacco Oud; Pepper and Roses; Gentle Flower; Come Back; Go Wild</t>
         </is>
@@ -2616,7 +2599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3195,6 +3178,78 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Fragrance World</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>first-copy house</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Designers Collection</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>first-copy house</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>World fragrance</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>first-copy house</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>first-copy house</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Testa</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/perfume_catalog.xlsx
+++ b/perfume_catalog.xlsx
@@ -3283,7 +3283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3292,6 +3292,11 @@
           <t>Brands</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -3374,6 +3379,498 @@
       <c r="A13" s="0" t="inlineStr">
         <is>
           <t>Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Clive Dorris Collection</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>first-copy house</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fragrance Deluxe</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>first-copy house</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Perfume Box</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>first-copy house</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Generic Xim</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Mini</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Beauty</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fragrance</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>women's</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Men'S</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VIP MEN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Versachem</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Versse</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Le Versant</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Lancom</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Giorgi</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dio</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Hermia</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dolcir</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Emporio</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Yves</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Yves St-Laurent</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Gu</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ZAT</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Bv</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dg</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ck</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>typosquat</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sauvage</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Black Opium</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Invictus</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Idole</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>My Way</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Asad</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hawas</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Shalimar</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Spice</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>product-name-as-brand</t>
         </is>
       </c>
     </row>

--- a/perfume_catalog.xlsx
+++ b/perfume_catalog.xlsx
@@ -3283,7 +3283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3292,7 +3292,7 @@
           <t>Brands</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>why</t>
         </is>
@@ -3383,492 +3383,468 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>Clive Dorris Collection</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>first-copy house</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>Fragrance Deluxe</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>first-copy house</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>Perfume Box</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>first-copy house</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>Generic Xim</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>Mini</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>Beauty</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>Fragrance</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>EDP</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>women's</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>Men'S</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>VIP MEN</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>Versachem</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>Versse</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>Le Versant</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>Lancom</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>Giorgi</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>Dio</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>Hermia</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>Dolcir</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>Emporio</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>Yves</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>Yves St-Laurent</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>Gu</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>ZAT</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>Bv</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>Dg</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>Ck</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>Sauvage</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>Black Opium</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>Invictus</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>Idole</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>My Way</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>Asad</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>Hawas</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Shalimar</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>product-name-as-brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>product-name-as-brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>Spice</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>

--- a/perfume_catalog.xlsx
+++ b/perfume_catalog.xlsx
@@ -3283,7 +3283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,7 +3397,7 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>Fragrance Deluxe</t>
+          <t>Perfume Box</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
@@ -3409,19 +3409,19 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t>Perfume Box</t>
+          <t>Generic Xim</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>first-copy house</t>
+          <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>Generic Xim</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
@@ -3433,7 +3433,7 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Fragrance</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
@@ -3457,7 +3457,7 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>Fragrance</t>
+          <t>EDP</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
@@ -3469,7 +3469,7 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>EDP</t>
+          <t>women's</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
@@ -3481,7 +3481,7 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>women's</t>
+          <t>Men'S</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
@@ -3493,7 +3493,7 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>Men'S</t>
+          <t>You</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
@@ -3505,7 +3505,7 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>VIP MEN</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
@@ -3517,19 +3517,19 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>VIP MEN</t>
+          <t>Versachem</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>typosquat</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>Versachem</t>
+          <t>Versse</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
@@ -3541,7 +3541,7 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t>Versse</t>
+          <t>Le Versant</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>Le Versant</t>
+          <t>Lancom</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
@@ -3565,7 +3565,7 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>Lancom</t>
+          <t>Giorgi</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
@@ -3577,7 +3577,7 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t>Giorgi</t>
+          <t>Dio</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>Dio</t>
+          <t>Hermia</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>Hermia</t>
+          <t>Dolcir</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
@@ -3613,7 +3613,7 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>Dolcir</t>
+          <t>Emporio</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>Emporio</t>
+          <t>Yves</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t>Yves</t>
+          <t>Yves St-Laurent</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
@@ -3649,7 +3649,7 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t>Yves St-Laurent</t>
+          <t>Gu</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t>Gu</t>
+          <t>ZAT</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
@@ -3673,7 +3673,7 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t>ZAT</t>
+          <t>Bv</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t>Bv</t>
+          <t>Dg</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
@@ -3697,7 +3697,7 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t>Dg</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
@@ -3709,7 +3709,7 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>Ck</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
@@ -3721,19 +3721,19 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t>Ck</t>
+          <t>Sauvage</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>typosquat</t>
+          <t>product-name-as-brand</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>Sauvage</t>
+          <t>Black Opium</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
@@ -3745,7 +3745,7 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t>Black Opium</t>
+          <t>Invictus</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
@@ -3757,7 +3757,7 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t>Invictus</t>
+          <t>Idole</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
@@ -3769,7 +3769,7 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t>Idole</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>My Way</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
@@ -3793,7 +3793,7 @@
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t>My Way</t>
+          <t>Asad</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
@@ -3805,7 +3805,7 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t>Asad</t>
+          <t>Hawas</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
@@ -3817,7 +3817,7 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t>Hawas</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
@@ -3829,22 +3829,10 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t>Now</t>
+          <t>Spice</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
-        <is>
-          <t>product-name-as-brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="0" t="inlineStr">
-        <is>
-          <t>Spice</t>
-        </is>
-      </c>
-      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>product-name-as-brand</t>
         </is>
